--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Statut de l'entrée provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
@@ -2615,13 +2618,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2639,7 +2642,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2656,10 +2659,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2685,10 +2688,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2739,7 +2742,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2756,10 +2759,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2785,10 +2788,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2839,7 +2842,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2856,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2882,13 +2885,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2939,7 +2942,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2956,10 +2959,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2982,13 +2985,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3039,7 +3042,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3051,15 +3054,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3082,13 +3085,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3139,7 +3142,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3156,14 +3159,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3182,16 +3185,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3229,19 +3232,19 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3253,19 +3256,19 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3278,25 +3281,25 @@
         <v>73</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3345,7 +3348,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3357,15 +3360,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3391,10 +3394,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3445,7 +3448,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3462,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3491,10 +3494,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3521,13 +3524,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3545,7 +3548,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3562,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3588,13 +3591,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3645,7 +3648,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3662,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3688,13 +3691,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3745,7 +3748,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3762,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3788,13 +3791,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3845,7 +3848,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3862,10 +3865,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3888,13 +3891,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3945,7 +3948,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
